--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484189_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484189_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5034</v>
+        <v>4.3525</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5078</v>
+        <v>2.2446</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9956</v>
+        <v>2.1079</v>
       </c>
       <c r="G2" t="n">
         <v>3.3019</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1258</v>
+        <v>0.9749</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1076</v>
+        <v>0.6293</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2334</v>
+        <v>0.3456</v>
       </c>
       <c r="V2" t="n">
         <v>0.8692</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3405</v>
+        <v>2.9187</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7224</v>
+        <v>1.3361</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.382</v>
+        <v>1.5827</v>
       </c>
       <c r="G3" t="n">
-        <v>0.971</v>
+        <v>1.1536</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.393</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1892</v>
+        <v>0.7605</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4875</v>
+        <v>1.3308</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4474</v>
+        <v>0.0456</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0402</v>
+        <v>1.2852</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5165</v>
+        <v>-0.1772</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6655</v>
+        <v>0.3474</v>
       </c>
       <c r="O3" t="n">
-        <v>0.149</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.7855</v>
+        <v>1.7855</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3968</v>
+        <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2144</v>
+        <v>-0.2863</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6074</v>
+        <v>-0.2607</v>
       </c>
       <c r="U3" t="n">
-        <v>0.607</v>
+        <v>-0.0256</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9405</v>
+        <v>0.266</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8097</v>
+        <v>0.266</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9227</v>
+        <v>2.4829</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1717</v>
+        <v>1.6808</v>
       </c>
       <c r="F4" t="n">
-        <v>1.751</v>
+        <v>0.8021</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1536</v>
+        <v>1.6964</v>
       </c>
       <c r="H4" t="n">
-        <v>0.393</v>
+        <v>2.2626</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7605</v>
+        <v>-0.5662</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3308</v>
+        <v>1.8606</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0456</v>
+        <v>1.371</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2852</v>
+        <v>0.4896</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1772</v>
+        <v>-0.1642</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3474</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-1.0558</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7855</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2823</v>
+        <v>-0.6264</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4251</v>
+        <v>-0.0056</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1428</v>
+        <v>-0.6207</v>
       </c>
       <c r="V4" t="n">
-        <v>0.266</v>
+        <v>1.8097</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>1.8097</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.685</v>
+        <v>1.9299</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9747</v>
+        <v>2.3961</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7104</v>
+        <v>-0.4661</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0572</v>
+        <v>0.971</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.513</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5442</v>
+        <v>0.1892</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.7846</v>
+        <v>1.4875</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4669</v>
+        <v>1.4474</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3177</v>
+        <v>0.0402</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2726</v>
+        <v>-0.5165</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.046</v>
+        <v>-0.6655</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2266</v>
+        <v>0.149</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7935</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>3.0795</v>
+        <v>1.8039</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6755</v>
+        <v>1.2811</v>
       </c>
       <c r="U5" t="n">
-        <v>0.404</v>
+        <v>0.5228</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8692</v>
+        <v>0.9405</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0757</v>
+        <v>1.8097</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1623</v>
+        <v>1.9107</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0911</v>
+        <v>-0.0061</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2534</v>
+        <v>1.9167</v>
       </c>
       <c r="G6" t="n">
         <v>0.4422</v>
@@ -922,13 +922,13 @@
         <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1925</v>
+        <v>0.9409</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7086</v>
+        <v>0.7936</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4839</v>
+        <v>0.1472</v>
       </c>
       <c r="V6" t="n">
         <v>-0.266</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7716</v>
+        <v>1.3655</v>
       </c>
       <c r="E7" t="n">
-        <v>1.25</v>
+        <v>0.1898</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5216</v>
+        <v>1.1757</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6964</v>
+        <v>-1.1862</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2626</v>
+        <v>1.3052</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5662</v>
+        <v>-2.4914</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8606</v>
+        <v>-0.3564</v>
       </c>
       <c r="K7" t="n">
-        <v>1.371</v>
+        <v>1.7594</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4896</v>
+        <v>-2.1158</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1642</v>
+        <v>-0.8298</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8915999999999999</v>
+        <v>-0.4542</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0558</v>
+        <v>-0.3756</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>-1.3887</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>2.1822</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3377</v>
+        <v>1.4922</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4364</v>
+        <v>1.0657</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9013</v>
+        <v>0.4264</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8097</v>
+        <v>0.266</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8097</v>
+        <v>0.8692</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3364</v>
+        <v>1.1288</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5868</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9232</v>
+        <v>0.4579</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1862</v>
+        <v>-2.0572</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3052</v>
+        <v>-0.513</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4914</v>
+        <v>-1.5442</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3564</v>
+        <v>-1.7846</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7594</v>
+        <v>-0.4669</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.1158</v>
+        <v>-1.3177</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8298</v>
+        <v>-0.2726</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4542</v>
+        <v>-0.046</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3756</v>
+        <v>-0.2266</v>
       </c>
       <c r="P8" t="n">
         <v>0.7935</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3887</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1822</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4631</v>
+        <v>1.5233</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2892</v>
+        <v>1.3718</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1739</v>
+        <v>0.1515</v>
       </c>
       <c r="V8" t="n">
-        <v>0.266</v>
+        <v>0.8692</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8692</v>
+        <v>2.0757</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6032</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0232</v>
+        <v>0.5538</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4074</v>
+        <v>-0.1014</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4307</v>
+        <v>0.6551</v>
       </c>
       <c r="G9" t="n">
         <v>0.0517</v>
@@ -1156,13 +1156,13 @@
         <v>0.1984</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0998</v>
+        <v>0.4308</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2494</v>
+        <v>0.0567</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1496</v>
+        <v>0.3741</v>
       </c>
       <c r="V9" t="n">
         <v>0.0713</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0187</v>
+        <v>0.1193</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2728</v>
+        <v>0.2332</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2542</v>
+        <v>-0.1139</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2202</v>
@@ -1234,13 +1234,13 @@
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3146</v>
+        <v>0.4152</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7029</v>
+        <v>0.6632</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3883</v>
+        <v>-0.248</v>
       </c>
       <c r="V10" t="n">
         <v>-0.266</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1379</v>
+        <v>-0.222</v>
       </c>
       <c r="E11" t="n">
         <v>-0.0623</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0755</v>
+        <v>-0.1597</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3312</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1933</v>
+        <v>0.1091</v>
       </c>
       <c r="T11" t="n">
         <v>-0.0623</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2556</v>
+        <v>0.1714</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.257</v>
+        <v>-0.9968</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3848</v>
+        <v>-0.1808</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8722</v>
+        <v>-0.8161</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3062</v>
@@ -1390,13 +1390,13 @@
         <v>2.1822</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5929</v>
+        <v>0.8531</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5896</v>
+        <v>0.7936</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0034</v>
+        <v>0.0595</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5437</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0021</v>
+        <v>-4.2412</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4954</v>
+        <v>-3.5942</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5067</v>
+        <v>-0.647</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8033</v>
@@ -1468,13 +1468,13 @@
         <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8815</v>
+        <v>-0.1205</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5384</v>
+        <v>0.3628</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.343</v>
+        <v>-0.4833</v>
       </c>
       <c r="V13" t="n">
         <v>0.0713</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.3668</v>
+        <v>11.3021</v>
       </c>
       <c r="E14" t="n">
-        <v>3.871599999999999</v>
+        <v>4.8067</v>
       </c>
       <c r="F14" t="n">
-        <v>6.495299999999999</v>
+        <v>6.4953</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2875000000000001</v>
+        <v>-0.287500000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>7.0321</v>
+        <v>7.032100000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-7.319500000000001</v>
@@ -1522,7 +1522,7 @@
         <v>5.010400000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>6.5334</v>
+        <v>6.533399999999999</v>
       </c>
       <c r="L14" t="n">
         <v>-1.523</v>
@@ -1531,7 +1531,7 @@
         <v>-5.297999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4989000000000003</v>
+        <v>0.4989000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-5.796800000000001</v>
@@ -1546,19 +1546,19 @@
         <v>17.8547</v>
       </c>
       <c r="S14" t="n">
-        <v>6.5748</v>
+        <v>7.510199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>5.754</v>
+        <v>6.6892</v>
       </c>
       <c r="U14" t="n">
-        <v>0.821</v>
+        <v>0.8208999999999997</v>
       </c>
       <c r="V14" t="n">
         <v>3.087499999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>9.969900000000001</v>
+        <v>9.969899999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-6.882499999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. TEJERO CASASAYAS</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0917</v>
+        <v>3.3955</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7495</v>
+        <v>3.5383</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3422</v>
+        <v>-0.1428</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1739</v>
+        <v>2.6837</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3733</v>
+        <v>0.5085</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1994</v>
+        <v>2.1752</v>
       </c>
       <c r="J15" t="n">
-        <v>1.251</v>
+        <v>2.9184</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6758999999999999</v>
+        <v>1.0282</v>
       </c>
       <c r="L15" t="n">
-        <v>0.575</v>
+        <v>1.8901</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4248</v>
+        <v>-0.2347</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0492</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3756</v>
+        <v>0.2851</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3806</v>
+        <v>1.5871</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3806</v>
+        <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0157</v>
+        <v>-0.6093</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0261</v>
+        <v>-0.2493</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0104</v>
+        <v>-0.36</v>
       </c>
       <c r="V15" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="W15" t="n">
         <v>0.8692</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.4724</v>
-      </c>
       <c r="X15" t="n">
-        <v>-0.6032</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>E. TEJERO CASASAYAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9415</v>
+        <v>3.3027</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4362</v>
+        <v>3.1373</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4948</v>
+        <v>0.1654</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6837</v>
+        <v>-0.1739</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5085</v>
+        <v>-0.3733</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1752</v>
+        <v>0.1994</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9184</v>
+        <v>1.251</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0282</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8901</v>
+        <v>0.575</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2347</v>
+        <v>-1.4248</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-1.0492</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2851</v>
+        <v>-0.3756</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5871</v>
+        <v>2.3806</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5871</v>
+        <v>2.3806</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0634</v>
+        <v>0.2268</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3514</v>
+        <v>0.4139</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.712</v>
+        <v>-0.1872</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.266</v>
+        <v>0.8692</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8692</v>
+        <v>1.4724</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1352</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9211</v>
+        <v>1.1073</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8762</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0448</v>
+        <v>0.129</v>
       </c>
       <c r="G17" t="n">
         <v>0.6325</v>
@@ -1780,13 +1780,13 @@
         <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4869</v>
+        <v>0.6731</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4422</v>
+        <v>0.5442</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0448</v>
+        <v>0.1289</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1216</v>
+        <v>0.1213</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8655</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9871</v>
+        <v>-0.5828</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2778</v>
+        <v>2.1415</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2097</v>
+        <v>0.1711</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4875</v>
+        <v>1.9705</v>
       </c>
       <c r="J18" t="n">
-        <v>1.578</v>
+        <v>2.4304</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3523</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9303</v>
+        <v>1.8149</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3002</v>
+        <v>-0.2888</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.4444</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5572</v>
+        <v>0.1555</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5871</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="S18" t="n">
-        <v>0.525</v>
+        <v>-1.417</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1281</v>
+        <v>-0.3457</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6031</v>
+        <v>-1.0714</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3373</v>
+        <v>-0.6032</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1352</v>
+        <v>0.6032</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7936</v>
+        <v>-0.3291</v>
       </c>
       <c r="E19" t="n">
-        <v>0.398</v>
+        <v>0.0493</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1916</v>
+        <v>-0.3784</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1415</v>
+        <v>1.2778</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1711</v>
+        <v>-1.2097</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9705</v>
+        <v>2.4875</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4304</v>
+        <v>1.578</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6153999999999999</v>
+        <v>-0.3523</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8149</v>
+        <v>1.9303</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2888</v>
+        <v>-0.3002</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4444</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1555</v>
+        <v>0.5572</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.3319</v>
+        <v>0.3175</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6518</v>
+        <v>0.3119</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6801</v>
+        <v>0.0056</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6032</v>
+        <v>-0.3373</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6032</v>
+        <v>1.1352</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MARBÀ RECASENS</t>
+          <t>C. FONS TEIXIDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.022</v>
+        <v>-1.7877</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5283</v>
+        <v>-0.5172</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4937</v>
+        <v>-1.2705</v>
       </c>
       <c r="G20" t="n">
-        <v>0.524</v>
+        <v>-0.0271</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2519</v>
+        <v>0.6751</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2721</v>
+        <v>-0.7023</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9879</v>
+        <v>0.8828</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9879</v>
+        <v>1.5981</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.7153</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4639</v>
+        <v>-0.91</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.736</v>
+        <v>-0.923</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2721</v>
+        <v>0.013</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3395</v>
+        <v>-1.1492</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.187</v>
+        <v>-0.408</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1525</v>
+        <v>-0.7412</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8097</v>
+        <v>-1.2065</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. FONS TEIXIDO</t>
+          <t>J. MARBÀ RECASENS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1796</v>
+        <v>-1.8341</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7212</v>
+        <v>-0.5283</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4584</v>
+        <v>-1.3058</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0271</v>
+        <v>0.524</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6751</v>
+        <v>0.2519</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7023</v>
+        <v>0.2721</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8828</v>
+        <v>0.9879</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5981</v>
+        <v>0.9879</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7153</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.91</v>
+        <v>-0.4639</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.923</v>
+        <v>-0.736</v>
       </c>
       <c r="O21" t="n">
-        <v>0.013</v>
+        <v>0.2721</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5952</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5412</v>
+        <v>-0.1516</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6121</v>
+        <v>-0.187</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9291</v>
+        <v>0.0354</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2065</v>
+        <v>-1.8097</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. BERNADÍ VALLS</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5936</v>
+        <v>-3.63</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.2718</v>
+        <v>-5.4261</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6782</v>
+        <v>1.7961</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.9728</v>
+        <v>-0.804</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.0014</v>
+        <v>-0.6199</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0286</v>
+        <v>-0.1841</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.4346</v>
+        <v>-0.9282</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.0355</v>
+        <v>-0.1804</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3991</v>
+        <v>-0.7478</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4618</v>
+        <v>0.1242</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0342</v>
+        <v>-0.4395</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4276</v>
+        <v>0.5637</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7935</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9838</v>
+        <v>-3.9677</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7774</v>
+        <v>1.9838</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4144</v>
+        <v>-0.7708</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0115</v>
+        <v>-0.459</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4258</v>
+        <v>-0.3119</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.0713</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1352</v>
+        <v>-0.0713</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>M. BERNADÍ VALLS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5319</v>
+        <v>-3.688</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6604</v>
+        <v>-5.5779</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8714</v>
+        <v>1.8899</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9942</v>
+        <v>-3.9728</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9606</v>
+        <v>-4.0014</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0337</v>
+        <v>0.0286</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8138</v>
+        <v>-4.4346</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-4.0355</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0829</v>
+        <v>-0.3991</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1804</v>
+        <v>0.4618</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0639</v>
+        <v>0.0342</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1165</v>
+        <v>0.4276</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1822</v>
+        <v>0.7935</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9677</v>
+        <v>-1.9838</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7855</v>
+        <v>2.7774</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6927</v>
+        <v>-0.5087</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3514</v>
+        <v>-0.2946</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3413</v>
+        <v>-0.2141</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4724</v>
+        <v>1.1352</v>
       </c>
       <c r="X23" t="n">
         <v>-1.1352</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0788</v>
+        <v>-4.304</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2423</v>
+        <v>-3.4564</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1636</v>
+        <v>-0.8476</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.804</v>
+        <v>-1.9942</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6199</v>
+        <v>-1.9606</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1841</v>
+        <v>-0.0337</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9282</v>
+        <v>-0.8138</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1804</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7478</v>
+        <v>0.0829</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1242</v>
+        <v>-1.1804</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4395</v>
+        <v>-1.0639</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5637</v>
+        <v>-0.1165</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q24" t="n">
         <v>-3.9677</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.2196</v>
+        <v>-0.4648</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2752</v>
+        <v>-0.1473</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9444</v>
+        <v>-0.3175</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.0713</v>
+        <v>0.3373</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0713</v>
+        <v>1.4724</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.3668</v>
+        <v>-7.646100000000001</v>
       </c>
       <c r="E25" t="n">
         <v>-7.098599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.268199999999999</v>
+        <v>-0.5475000000000002</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2875000000000001</v>
+        <v>0.2874999999999994</v>
       </c>
       <c r="H25" t="n">
         <v>-7.0322</v>
@@ -2377,10 +2377,10 @@
         <v>7.319599999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>5.297899999999999</v>
+        <v>5.297900000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4989</v>
+        <v>-0.4988999999999999</v>
       </c>
       <c r="L25" t="n">
         <v>5.7965</v>
@@ -2404,22 +2404,22 @@
         <v>16.8627</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.575100000000001</v>
+        <v>-3.854</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8209999999999997</v>
+        <v>-0.8209</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.7539</v>
+        <v>-3.0334</v>
       </c>
       <c r="V25" t="n">
         <v>-3.0875</v>
       </c>
       <c r="W25" t="n">
-        <v>6.279000000000001</v>
+        <v>6.279</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.3666</v>
+        <v>-9.366599999999998</v>
       </c>
     </row>
   </sheetData>
